--- a/id_reference.xlsx
+++ b/id_reference.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Games\Steam\steamapps\common\Anno 117 - Pax Romana\mods\[Gameplay] Celtic Independence Overhaul (Jtmzac)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292F665F-66ED-4561-8558-EB69AB213BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4C6DF0-0FD8-457B-9A0F-BEBE682673A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28050" yWindow="615" windowWidth="24315" windowHeight="15210" xr2:uid="{F096A854-2640-4D9E-B630-929558042427}"/>
+    <workbookView xWindow="-28095" yWindow="150" windowWidth="24150" windowHeight="15525" xr2:uid="{F096A854-2640-4D9E-B630-929558042427}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -795,7 +795,7 @@
         <v>720</v>
       </c>
       <c r="D21">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.35">
@@ -812,11 +812,11 @@
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D25">
         <f>D21-C2</f>
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E25">
         <f>D25-F25</f>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F25">
         <f>SUM(F2:F20)</f>
